--- a/grupos/4APM - Estadisticos 20232.xlsx
+++ b/grupos/4APM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -206,21 +206,21 @@
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Hernández López Elizabeth</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Hernández Castro Enrique</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,34 +233,34 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CORRO</t>
+  </si>
+  <si>
+    <t>OLMEDO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>LUNA</t>
@@ -269,58 +269,28 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
     <t>ALFONSO</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
+    <t>MIGUEL ANGEL</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>DINORAH AZUL</t>
+  </si>
+  <si>
+    <t>SERGIO FARITH</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
   </si>
   <si>
     <t>SAUL KOURCHENKOV</t>
   </si>
   <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>FERNANDA ANGELICA</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>KAY LEILANI</t>
-  </si>
-  <si>
     <t>JULIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
 </sst>
 </file>
@@ -847,25 +817,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -898,7 +868,7 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>9</v>
@@ -936,25 +906,25 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -993,10 +963,10 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1025,25 +995,25 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1070,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1079,13 +1049,13 @@
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1114,25 +1084,25 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1165,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>9</v>
@@ -1203,25 +1173,25 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1248,19 +1218,19 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -1292,25 +1262,25 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1334,10 +1304,10 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1352,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1381,25 +1351,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1423,7 +1393,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1432,7 +1402,7 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <v>9</v>
@@ -1470,25 +1440,25 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1515,22 +1485,22 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>8</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1559,25 +1529,25 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1604,22 +1574,22 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1648,25 +1618,25 @@
         <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1690,25 +1660,25 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1737,25 +1707,25 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1785,7 +1755,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1794,7 +1764,7 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1826,25 +1796,25 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1871,22 +1841,22 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1915,25 +1885,25 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1960,22 +1930,22 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1995,7 +1965,7 @@
         <v>8</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>9</v>
@@ -2004,25 +1974,25 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2058,13 +2028,13 @@
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2084,7 +2054,7 @@
         <v>9</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -2093,25 +2063,25 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2138,22 +2108,22 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2182,25 +2152,25 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2227,19 +2197,19 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>10</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -2271,25 +2241,25 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2316,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2325,10 +2295,10 @@
         <v>8</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2360,25 +2330,25 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2402,22 +2372,22 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2449,25 +2419,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2494,19 +2464,19 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>10</v>
@@ -2538,25 +2508,25 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2583,7 +2553,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2592,13 +2562,13 @@
         <v>7</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2627,25 +2597,25 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2669,25 +2639,25 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2716,25 +2686,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2758,22 +2728,22 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA25">
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2805,25 +2775,25 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2847,7 +2817,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2856,16 +2826,16 @@
         <v>5</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2894,25 +2864,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2936,19 +2906,19 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -2983,25 +2953,25 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3028,19 +2998,19 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>9</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA28">
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC28">
         <v>10</v>
@@ -3072,25 +3042,25 @@
         <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3123,13 +3093,13 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>7</v>
@@ -3161,25 +3131,25 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3209,19 +3179,19 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3250,25 +3220,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3295,19 +3265,19 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3339,25 +3309,25 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3381,10 +3351,10 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3396,10 +3366,10 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3428,25 +3398,25 @@
         <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3473,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3482,10 +3452,10 @@
         <v>6</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC33">
         <v>7</v>
@@ -3517,25 +3487,25 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3559,19 +3529,19 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB34">
         <v>10</v>
@@ -3606,25 +3576,25 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3648,7 +3618,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3663,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC35">
         <v>10</v>
@@ -3695,25 +3665,25 @@
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3740,22 +3710,22 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <v>5</v>
       </c>
       <c r="AA36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -3784,25 +3754,25 @@
         <v>7</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3826,10 +3796,10 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>7</v>
@@ -3841,10 +3811,10 @@
         <v>10</v>
       </c>
       <c r="AB37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3873,25 +3843,25 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3927,10 +3897,10 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC38">
         <v>5</v>
@@ -4155,7 +4125,7 @@
         <v>90</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="K5">
         <v>83.3</v>
@@ -4164,19 +4134,19 @@
         <v>80</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N5">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="P5">
         <v>90</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="R5">
         <v>83.3</v>
@@ -4185,13 +4155,13 @@
         <v>80</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="U5">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="V5">
-        <v>100</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4356,16 +4326,16 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4377,16 +4347,16 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4424,7 +4394,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -4433,7 +4403,7 @@
         <v>93.3</v>
       </c>
       <c r="L9">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -4445,7 +4415,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4454,7 +4424,7 @@
         <v>93.3</v>
       </c>
       <c r="S9">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4501,7 +4471,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -4522,7 +4492,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4563,13 +4533,13 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -4578,19 +4548,19 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>68.8</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4599,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4628,7 +4598,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4649,7 +4619,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4696,16 +4666,16 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="J13">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="K13">
         <v>83.3</v>
       </c>
       <c r="L13">
-        <v>80</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -4717,16 +4687,16 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="Q13">
-        <v>75</v>
+        <v>77.5</v>
       </c>
       <c r="R13">
         <v>83.3</v>
       </c>
       <c r="S13">
-        <v>80</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4764,13 +4734,13 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>85</v>
+        <v>72.5</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="K14">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="L14">
         <v>80</v>
@@ -4785,13 +4755,13 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>85</v>
+        <v>72.5</v>
       </c>
       <c r="Q14">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="R14">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="S14">
         <v>80</v>
@@ -4832,16 +4802,16 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L15">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -4853,16 +4823,16 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R15">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S15">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -4900,16 +4870,16 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -4921,16 +4891,16 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -4968,7 +4938,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4989,7 +4959,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5036,7 +5006,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -5057,7 +5027,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5107,10 +5077,10 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K19">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5128,10 +5098,10 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R19">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5172,7 +5142,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -5181,7 +5151,7 @@
         <v>96.7</v>
       </c>
       <c r="L20">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -5193,7 +5163,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5202,7 +5172,7 @@
         <v>96.7</v>
       </c>
       <c r="S20">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -5308,7 +5278,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -5329,7 +5299,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5382,10 +5352,10 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -5403,10 +5373,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5450,10 +5420,10 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L24">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -5471,10 +5441,10 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="S24">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5580,7 +5550,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -5589,7 +5559,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -5601,7 +5571,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5610,7 +5580,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5716,7 +5686,7 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="J28">
         <v>100</v>
@@ -5737,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5787,13 +5757,13 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K29">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L29">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5808,13 +5778,13 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="R29">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="S29">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5923,10 +5893,10 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L31">
         <v>94.3</v>
@@ -5944,10 +5914,10 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S31">
         <v>94.3</v>
@@ -5991,13 +5961,13 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K32">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L32">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="M32">
         <v>100</v>
@@ -6012,13 +5982,13 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="R32">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="S32">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6062,10 +6032,10 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -6083,10 +6053,10 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="T33">
         <v>100</v>
@@ -6198,10 +6168,10 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -6219,10 +6189,10 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6260,17 +6230,17 @@
         <v>100</v>
       </c>
       <c r="I36">
+        <v>95</v>
+      </c>
+      <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
+        <v>98.3</v>
+      </c>
+      <c r="L36">
         <v>90</v>
       </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
-      <c r="K36">
-        <v>100</v>
-      </c>
-      <c r="L36">
-        <v>88.59999999999999</v>
-      </c>
       <c r="M36">
         <v>100</v>
       </c>
@@ -6281,16 +6251,16 @@
         <v>100</v>
       </c>
       <c r="P36">
+        <v>95</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
+        <v>98.3</v>
+      </c>
+      <c r="S36">
         <v>90</v>
-      </c>
-      <c r="Q36">
-        <v>100</v>
-      </c>
-      <c r="R36">
-        <v>100</v>
-      </c>
-      <c r="S36">
-        <v>88.59999999999999</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6331,13 +6301,13 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M37">
         <v>100</v>
@@ -6352,13 +6322,13 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R37">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6396,13 +6366,13 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K38">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="L38">
         <v>85.7</v>
@@ -6411,19 +6381,19 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="O38">
         <v>100</v>
       </c>
       <c r="P38">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="Q38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="R38">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="S38">
         <v>85.7</v>
@@ -6432,7 +6402,7 @@
         <v>100</v>
       </c>
       <c r="U38">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="V38">
         <v>100</v>
@@ -6501,19 +6471,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>54.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>45.7</v>
+        <v>22.9</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6545,7 +6515,7 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6556,7 +6526,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -6577,7 +6547,7 @@
         <v>14.3</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6588,7 +6558,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -6597,19 +6567,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>91.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>8.6</v>
+        <v>11.4</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6641,7 +6611,7 @@
         <v>8.6</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6652,7 +6622,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -6661,19 +6631,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="G7" s="2">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6684,7 +6654,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
@@ -6693,19 +6663,19 @@
         <v>35</v>
       </c>
       <c r="D8">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6755,7 +6725,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6787,22 +6757,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920112</v>
+        <v>22330051920153</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6810,22 +6780,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920112</v>
+        <v>22330051920153</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6833,22 +6803,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920386</v>
+        <v>21330051920112</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6856,22 +6826,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920386</v>
+        <v>21330051920112</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6879,16 +6849,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920282</v>
+        <v>22330051920162</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6902,16 +6872,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920282</v>
+        <v>22330051920162</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6925,16 +6895,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920151</v>
+        <v>22330051920367</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6948,22 +6918,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920155</v>
+        <v>22330051920367</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6971,22 +6941,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051420487</v>
+        <v>22330051920386</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6994,16 +6964,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920299</v>
+        <v>22330051920386</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -7017,22 +6987,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920164</v>
+        <v>22330051920282</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7040,22 +7010,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920167</v>
+        <v>22330051920282</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7066,13 +7036,13 @@
         <v>22330051920170</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -7081,29 +7051,6 @@
         <v>60</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920172</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4APM - Estadisticos 20232.xlsx
+++ b/grupos/4APM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -203,15 +203,15 @@
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
+    <t>Hernández López Elizabeth</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Hernández López Elizabeth</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -233,64 +233,37 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
+    <t>QUINTANA</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>SERGIO FARITH</t>
+    <t>JULIO</t>
   </si>
   <si>
     <t>GUSTAVO</t>
   </si>
   <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>JULIO</t>
+    <t>CRISTIAN</t>
   </si>
 </sst>
 </file>
@@ -838,25 +811,25 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -927,25 +900,25 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1016,25 +989,25 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1043,19 +1016,19 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1099,31 +1072,31 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1132,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1141,7 +1114,7 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1194,28 +1167,28 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1283,46 +1256,46 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1372,25 +1345,25 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1399,7 +1372,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1461,37 +1434,37 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1550,34 +1523,34 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>10</v>
@@ -1586,7 +1559,7 @@
         <v>9</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>10</v>
@@ -1639,25 +1612,25 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1669,16 +1642,16 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1728,25 +1701,25 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1764,7 +1737,7 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1817,28 +1790,28 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1847,16 +1820,16 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1906,40 +1879,40 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>6</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -1995,31 +1968,31 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2028,10 +2001,10 @@
         <v>8</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>9</v>
@@ -2084,25 +2057,25 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2111,13 +2084,13 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>8</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>9</v>
@@ -2173,43 +2146,43 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>10</v>
@@ -2262,25 +2235,25 @@
         <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2289,16 +2262,16 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2351,25 +2324,25 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2384,10 +2357,10 @@
         <v>9</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2440,28 +2413,28 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2473,7 +2446,7 @@
         <v>9</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>10</v>
@@ -2529,37 +2502,37 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>6</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2618,43 +2591,43 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2707,25 +2680,25 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2734,7 +2707,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -2743,7 +2716,7 @@
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>10</v>
@@ -2796,40 +2769,40 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -2885,25 +2858,25 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2912,7 +2885,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -2974,34 +2947,34 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>9</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>9</v>
@@ -3063,28 +3036,28 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -3096,10 +3069,10 @@
         <v>7</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC29">
         <v>7</v>
@@ -3152,25 +3125,25 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3179,7 +3152,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3188,10 +3161,10 @@
         <v>7</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3241,28 +3214,28 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3271,13 +3244,13 @@
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>9</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3330,25 +3303,25 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>8</v>
@@ -3363,13 +3336,13 @@
         <v>9</v>
       </c>
       <c r="AA32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3419,43 +3392,43 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC33">
         <v>7</v>
@@ -3508,25 +3481,25 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3535,10 +3508,10 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA34">
         <v>9</v>
@@ -3597,28 +3570,28 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3630,7 +3603,7 @@
         <v>6</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>9</v>
@@ -3686,25 +3659,25 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3713,13 +3686,13 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB36">
         <v>9</v>
@@ -3775,37 +3748,37 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>7</v>
       </c>
       <c r="Z37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>10</v>
@@ -3864,46 +3837,46 @@
         <v>5</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>5</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4143,25 +4116,25 @@
         <v>81.3</v>
       </c>
       <c r="P5">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="R5">
         <v>83.3</v>
       </c>
       <c r="S5">
-        <v>80</v>
+        <v>58.9</v>
       </c>
       <c r="T5">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="U5">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="V5">
         <v>87.5</v>
-      </c>
-      <c r="U5">
-        <v>95.5</v>
-      </c>
-      <c r="V5">
-        <v>81.3</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4347,16 +4320,16 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S8">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -4415,16 +4388,16 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R9">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="S9">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -4492,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -4548,19 +4521,19 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>68.8</v>
+        <v>100</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S11">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -4569,7 +4542,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>68.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4619,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4687,16 +4660,16 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="Q13">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R13">
-        <v>83.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="S13">
-        <v>82.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -4755,25 +4728,25 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>72.5</v>
+        <v>60.9</v>
       </c>
       <c r="Q14">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="R14">
-        <v>91.7</v>
+        <v>62.5</v>
       </c>
       <c r="S14">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="T14">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V14">
-        <v>100</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4823,16 +4796,16 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R15">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S15">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T15">
         <v>100</v>
@@ -4891,19 +4864,19 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R16">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4959,7 +4932,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5027,13 +5000,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5095,13 +5068,13 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5163,16 +5136,16 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S20">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -5237,7 +5210,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -5299,13 +5272,13 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5373,10 +5346,10 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S23">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -5438,13 +5411,13 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R24">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S24">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -5503,7 +5476,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5571,16 +5544,16 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S26">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5639,7 +5612,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5707,7 +5680,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5775,16 +5748,16 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="R29">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="S29">
-        <v>92.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5843,16 +5816,16 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q30">
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -5911,16 +5884,16 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q31">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R31">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S31">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="T31">
         <v>100</v>
@@ -5979,16 +5952,16 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q32">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R32">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="S32">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6047,19 +6020,19 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="S33">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="U33">
         <v>100</v>
@@ -6115,7 +6088,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -6183,16 +6156,16 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q35">
         <v>100</v>
       </c>
       <c r="R35">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S35">
-        <v>95.7</v>
+        <v>93.8</v>
       </c>
       <c r="T35">
         <v>100</v>
@@ -6251,16 +6224,16 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q36">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R36">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S36">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6322,13 +6295,13 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R37">
-        <v>98.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S37">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="T37">
         <v>100</v>
@@ -6387,22 +6360,22 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="Q38">
-        <v>80</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R38">
-        <v>93.3</v>
+        <v>94.8</v>
       </c>
       <c r="S38">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="T38">
         <v>100</v>
       </c>
       <c r="U38">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="V38">
         <v>100</v>
@@ -6471,19 +6444,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>77.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="G2" s="2">
-        <v>22.9</v>
+        <v>14.3</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6494,7 +6467,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -6503,19 +6476,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>80</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>20</v>
+        <v>8.6</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6535,19 +6508,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>85.7</v>
+        <v>94.3</v>
       </c>
       <c r="G4" s="2">
-        <v>14.3</v>
+        <v>5.7</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6558,7 +6531,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -6567,19 +6540,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="G5" s="2">
-        <v>11.4</v>
+        <v>5.7</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6599,19 +6572,19 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>91.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="G6" s="2">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6631,16 +6604,16 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="H7">
         <v>8.300000000000001</v>
@@ -6675,7 +6648,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6725,7 +6698,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6757,22 +6730,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920153</v>
+        <v>21330051920112</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>84</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6780,22 +6753,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920153</v>
+        <v>22330051920170</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6803,16 +6776,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920112</v>
+        <v>22330051920386</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6826,231 +6799,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920112</v>
+        <v>22330051920426</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>61</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920162</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920162</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920367</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920367</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920386</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920386</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920282</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920282</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920170</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>
